--- a/machine_learning/pspeo_master.xlsx
+++ b/machine_learning/pspeo_master.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="218">
   <si>
     <t xml:space="preserve">Sample</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">afm_grain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tri</t>
   </si>
   <si>
     <t xml:space="preserve">I_A_AC</t>
@@ -773,7 +776,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I203"/>
-  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="2.26"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -800,16 +806,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -832,13 +841,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1.25</v>
@@ -856,18 +865,18 @@
         <v>0.0047</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1.5</v>
@@ -885,18 +894,18 @@
         <v>0.0534</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1.75</v>
@@ -914,18 +923,18 @@
         <v>0.0425</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>2</v>
@@ -943,18 +952,18 @@
         <v>0.0244</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>2.25</v>
@@ -972,18 +981,18 @@
         <v>0.1137</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>2.5</v>
@@ -1001,18 +1010,18 @@
         <v>0.0907</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>2.75</v>
@@ -1030,18 +1039,18 @@
         <v>0.1287</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
@@ -1059,18 +1068,18 @@
         <v>0.0617</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>3.25</v>
@@ -1088,18 +1097,18 @@
         <v>0.3226</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>3.5</v>
@@ -1117,18 +1126,18 @@
         <v>0.0892</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>3.75</v>
@@ -1146,18 +1155,18 @@
         <v>0.0795</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>4</v>
@@ -1175,18 +1184,18 @@
         <v>0.0987</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>4.25</v>
@@ -1204,18 +1213,18 @@
         <v>0.2132</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>4.5</v>
@@ -1233,18 +1242,18 @@
         <v>0.111</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>4.75</v>
@@ -1262,18 +1271,18 @@
         <v>0.1188</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>5</v>
@@ -1291,18 +1300,18 @@
         <v>0.2669</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>5.25</v>
@@ -1320,18 +1329,18 @@
         <v>0.2157</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>5.5</v>
@@ -1349,18 +1358,18 @@
         <v>0.1838</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>5.75</v>
@@ -1378,18 +1387,18 @@
         <v>0.2041</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>6</v>
@@ -1407,18 +1416,18 @@
         <v>0.1738</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>6.25</v>
@@ -1436,18 +1445,18 @@
         <v>0.2165</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>6.5</v>
@@ -1465,18 +1474,18 @@
         <v>0.3211</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>6.75</v>
@@ -1494,18 +1503,18 @@
         <v>0.233</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>7</v>
@@ -1523,18 +1532,18 @@
         <v>0.715</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>1</v>
@@ -1557,13 +1566,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>1.25</v>
@@ -1581,18 +1590,18 @@
         <v>0.0049</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>1.5</v>
@@ -1610,18 +1619,18 @@
         <v>0.0183</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>1.75</v>
@@ -1639,18 +1648,18 @@
         <v>0.0144</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>2</v>
@@ -1668,18 +1677,18 @@
         <v>0.0477</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>2.25</v>
@@ -1697,18 +1706,18 @@
         <v>0.1473</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>2.5</v>
@@ -1726,18 +1735,18 @@
         <v>0.1068</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>2.75</v>
@@ -1755,18 +1764,18 @@
         <v>0.066</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>3</v>
@@ -1784,18 +1793,18 @@
         <v>0.1334</v>
       </c>
       <c r="I35" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>3.25</v>
@@ -1813,18 +1822,18 @@
         <v>0.0698</v>
       </c>
       <c r="I36" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>3.5</v>
@@ -1842,18 +1851,18 @@
         <v>0.0932</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>3.75</v>
@@ -1871,18 +1880,18 @@
         <v>0.1233</v>
       </c>
       <c r="I38" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>4</v>
@@ -1900,18 +1909,18 @@
         <v>0.1492</v>
       </c>
       <c r="I39" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>4.25</v>
@@ -1929,18 +1938,18 @@
         <v>0.1048</v>
       </c>
       <c r="I40" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>4.5</v>
@@ -1958,18 +1967,18 @@
         <v>0.0795</v>
       </c>
       <c r="I41" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>4.75</v>
@@ -1987,18 +1996,18 @@
         <v>0.1302</v>
       </c>
       <c r="I42" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>5</v>
@@ -2016,18 +2025,18 @@
         <v>0.1078</v>
       </c>
       <c r="I43" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>5.25</v>
@@ -2045,18 +2054,18 @@
         <v>0.1004</v>
       </c>
       <c r="I44" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>5.5</v>
@@ -2074,18 +2083,18 @@
         <v>0.1656</v>
       </c>
       <c r="I45" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>5.75</v>
@@ -2103,18 +2112,18 @@
         <v>0.1026</v>
       </c>
       <c r="I46" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>6</v>
@@ -2132,18 +2141,18 @@
         <v>0.0895</v>
       </c>
       <c r="I47" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>6.25</v>
@@ -2161,18 +2170,18 @@
         <v>0.0833</v>
       </c>
       <c r="I48" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>6.5</v>
@@ -2190,18 +2199,18 @@
         <v>0.1417</v>
       </c>
       <c r="I49" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>6.75</v>
@@ -2219,18 +2228,18 @@
         <v>0.2062</v>
       </c>
       <c r="I50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>7</v>
@@ -2248,18 +2257,18 @@
         <v>0.2381</v>
       </c>
       <c r="I51" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>1</v>
@@ -2282,13 +2291,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C53" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>1.25</v>
@@ -2306,18 +2315,18 @@
         <v>0.0069</v>
       </c>
       <c r="I53" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>1.5</v>
@@ -2335,18 +2344,18 @@
         <v>0.0289</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>1.75</v>
@@ -2364,18 +2373,18 @@
         <v>0.0532</v>
       </c>
       <c r="I55" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>2</v>
@@ -2393,18 +2402,18 @@
         <v>0.0372</v>
       </c>
       <c r="I56" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>2.25</v>
@@ -2422,18 +2431,18 @@
         <v>0.1171</v>
       </c>
       <c r="I57" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>2.5</v>
@@ -2451,18 +2460,18 @@
         <v>0.0598</v>
       </c>
       <c r="I58" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>2.75</v>
@@ -2480,18 +2489,18 @@
         <v>0.0649</v>
       </c>
       <c r="I59" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>3</v>
@@ -2509,18 +2518,18 @@
         <v>0.1736</v>
       </c>
       <c r="I60" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>3.25</v>
@@ -2538,18 +2547,18 @@
         <v>0.113</v>
       </c>
       <c r="I61" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>3.5</v>
@@ -2567,18 +2576,18 @@
         <v>0.0775</v>
       </c>
       <c r="I62" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>3.75</v>
@@ -2596,18 +2605,18 @@
         <v>0.1896</v>
       </c>
       <c r="I63" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>4</v>
@@ -2625,18 +2634,18 @@
         <v>0.3651</v>
       </c>
       <c r="I64" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>4.25</v>
@@ -2654,18 +2663,18 @@
         <v>0.2267</v>
       </c>
       <c r="I65" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D66" s="1" t="n">
         <v>4.5</v>
@@ -2683,18 +2692,18 @@
         <v>0.0604</v>
       </c>
       <c r="I66" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>4.75</v>
@@ -2712,18 +2721,18 @@
         <v>0.1878</v>
       </c>
       <c r="I67" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D68" s="1" t="n">
         <v>5</v>
@@ -2741,18 +2750,18 @@
         <v>0.0898</v>
       </c>
       <c r="I68" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D69" s="1" t="n">
         <v>5.25</v>
@@ -2770,18 +2779,18 @@
         <v>0.1235</v>
       </c>
       <c r="I69" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D70" s="1" t="n">
         <v>5.5</v>
@@ -2799,18 +2808,18 @@
         <v>0.3767</v>
       </c>
       <c r="I70" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D71" s="1" t="n">
         <v>5.75</v>
@@ -2828,18 +2837,18 @@
         <v>0.1257</v>
       </c>
       <c r="I71" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D72" s="1" t="n">
         <v>6</v>
@@ -2857,18 +2866,18 @@
         <v>0.1012</v>
       </c>
       <c r="I72" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D73" s="1" t="n">
         <v>6.25</v>
@@ -2886,18 +2895,18 @@
         <v>0.3471</v>
       </c>
       <c r="I73" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D74" s="1" t="n">
         <v>6.5</v>
@@ -2915,18 +2924,18 @@
         <v>0.2093</v>
       </c>
       <c r="I74" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" s="1" t="n">
         <v>6.75</v>
@@ -2944,18 +2953,18 @@
         <v>0.2126</v>
       </c>
       <c r="I75" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" s="1" t="n">
         <v>7</v>
@@ -2973,18 +2982,18 @@
         <v>0.1338</v>
       </c>
       <c r="I76" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D77" s="1" t="n">
         <v>1</v>
@@ -3007,13 +3016,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C78" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D78" s="1" t="n">
         <v>1.25</v>
@@ -3031,18 +3040,18 @@
         <v>0.0072</v>
       </c>
       <c r="I78" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>1.5</v>
@@ -3060,18 +3069,18 @@
         <v>0.0569</v>
       </c>
       <c r="I79" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>1.75</v>
@@ -3089,18 +3098,18 @@
         <v>0.0335</v>
       </c>
       <c r="I80" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>2</v>
@@ -3123,13 +3132,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>2.25</v>
@@ -3147,18 +3156,18 @@
         <v>0.0582</v>
       </c>
       <c r="I82" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>2.5</v>
@@ -3176,18 +3185,18 @@
         <v>0.0919</v>
       </c>
       <c r="I83" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>2.75</v>
@@ -3205,18 +3214,18 @@
         <v>0.1962</v>
       </c>
       <c r="I84" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>3</v>
@@ -3234,18 +3243,18 @@
         <v>0.1931</v>
       </c>
       <c r="I85" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>3.25</v>
@@ -3263,18 +3272,18 @@
         <v>0.0469</v>
       </c>
       <c r="I86" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D87" s="1" t="n">
         <v>3.5</v>
@@ -3292,18 +3301,18 @@
         <v>0.1478</v>
       </c>
       <c r="I87" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>3.75</v>
@@ -3321,18 +3330,18 @@
         <v>0.1083</v>
       </c>
       <c r="I88" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>4</v>
@@ -3350,18 +3359,18 @@
         <v>0.2201</v>
       </c>
       <c r="I89" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>4.25</v>
@@ -3379,18 +3388,18 @@
         <v>0.2012</v>
       </c>
       <c r="I90" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>4.5</v>
@@ -3408,18 +3417,18 @@
         <v>0.2235</v>
       </c>
       <c r="I91" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>4.75</v>
@@ -3437,18 +3446,18 @@
         <v>0.1453</v>
       </c>
       <c r="I92" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>5</v>
@@ -3466,18 +3475,18 @@
         <v>0.1342</v>
       </c>
       <c r="I93" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D94" s="1" t="n">
         <v>5.25</v>
@@ -3495,18 +3504,18 @@
         <v>0.1107</v>
       </c>
       <c r="I94" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>5.5</v>
@@ -3524,18 +3533,18 @@
         <v>0.1416</v>
       </c>
       <c r="I95" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>5.75</v>
@@ -3553,18 +3562,18 @@
         <v>0.3162</v>
       </c>
       <c r="I96" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D97" s="1" t="n">
         <v>6</v>
@@ -3582,18 +3591,18 @@
         <v>0.1379</v>
       </c>
       <c r="I97" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>6.25</v>
@@ -3611,18 +3620,18 @@
         <v>0.2425</v>
       </c>
       <c r="I98" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D99" s="1" t="n">
         <v>6.5</v>
@@ -3640,18 +3649,18 @@
         <v>0.1371</v>
       </c>
       <c r="I99" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D100" s="1" t="n">
         <v>6.75</v>
@@ -3669,18 +3678,18 @@
         <v>0.2218</v>
       </c>
       <c r="I100" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D101" s="1" t="n">
         <v>7</v>
@@ -3698,18 +3707,18 @@
         <v>0.024</v>
       </c>
       <c r="I101" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D102" s="1" t="n">
         <v>1</v>
@@ -3732,13 +3741,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="C103" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D103" s="1" t="n">
         <v>1.25</v>
@@ -3756,18 +3765,18 @@
         <v>0.039</v>
       </c>
       <c r="I103" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D104" s="1" t="n">
         <v>1.5</v>
@@ -3785,18 +3794,18 @@
         <v>0.0351</v>
       </c>
       <c r="I104" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D105" s="1" t="n">
         <v>1.75</v>
@@ -3814,18 +3823,18 @@
         <v>0.0295</v>
       </c>
       <c r="I105" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>2</v>
@@ -3848,13 +3857,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D107" s="1" t="n">
         <v>2.25</v>
@@ -3872,18 +3881,18 @@
         <v>0.0971</v>
       </c>
       <c r="I107" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D108" s="1" t="n">
         <v>2.5</v>
@@ -3901,18 +3910,18 @@
         <v>0.0641</v>
       </c>
       <c r="I108" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D109" s="1" t="n">
         <v>2.75</v>
@@ -3930,18 +3939,18 @@
         <v>0.1118</v>
       </c>
       <c r="I109" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D110" s="1" t="n">
         <v>3</v>
@@ -3959,18 +3968,18 @@
         <v>0.0785</v>
       </c>
       <c r="I110" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D111" s="1" t="n">
         <v>3.25</v>
@@ -3988,18 +3997,18 @@
         <v>0.1225</v>
       </c>
       <c r="I111" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>3.5</v>
@@ -4017,18 +4026,18 @@
         <v>0.1531</v>
       </c>
       <c r="I112" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D113" s="1" t="n">
         <v>3.75</v>
@@ -4046,18 +4055,18 @@
         <v>0.2107</v>
       </c>
       <c r="I113" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>4</v>
@@ -4075,18 +4084,18 @@
         <v>0.259</v>
       </c>
       <c r="I114" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>4.25</v>
@@ -4104,18 +4113,18 @@
         <v>0.5903</v>
       </c>
       <c r="I115" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>4.5</v>
@@ -4133,18 +4142,18 @@
         <v>0.3177</v>
       </c>
       <c r="I116" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>4.75</v>
@@ -4162,18 +4171,18 @@
         <v>0.322</v>
       </c>
       <c r="I117" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>5</v>
@@ -4191,18 +4200,18 @@
         <v>0.1332</v>
       </c>
       <c r="I118" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D119" s="1" t="n">
         <v>5.25</v>
@@ -4220,18 +4229,18 @@
         <v>0.1843</v>
       </c>
       <c r="I119" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>5.5</v>
@@ -4249,18 +4258,18 @@
         <v>0.1043</v>
       </c>
       <c r="I120" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>5.75</v>
@@ -4278,18 +4287,18 @@
         <v>0.1688</v>
       </c>
       <c r="I121" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>6</v>
@@ -4307,18 +4316,18 @@
         <v>0.1397</v>
       </c>
       <c r="I122" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>6.25</v>
@@ -4336,18 +4345,18 @@
         <v>0.217</v>
       </c>
       <c r="I123" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>6.5</v>
@@ -4365,18 +4374,18 @@
         <v>0.3731</v>
       </c>
       <c r="I124" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>6.75</v>
@@ -4394,18 +4403,18 @@
         <v>0.808</v>
       </c>
       <c r="I125" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>7</v>
@@ -4423,18 +4432,18 @@
         <v>0.0305</v>
       </c>
       <c r="I126" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>1</v>
@@ -4457,13 +4466,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C128" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>1.25</v>
@@ -4481,18 +4490,18 @@
         <v>0.0215</v>
       </c>
       <c r="I128" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>1.5</v>
@@ -4510,18 +4519,18 @@
         <v>0.0578</v>
       </c>
       <c r="I129" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>1.75</v>
@@ -4544,13 +4553,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>2</v>
@@ -4568,18 +4577,18 @@
         <v>0.0594</v>
       </c>
       <c r="I131" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>2.25</v>
@@ -4597,18 +4606,18 @@
         <v>0.0407</v>
       </c>
       <c r="I132" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>2.5</v>
@@ -4626,18 +4635,18 @@
         <v>0.2223</v>
       </c>
       <c r="I133" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>2.75</v>
@@ -4655,18 +4664,18 @@
         <v>0.1631</v>
       </c>
       <c r="I134" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>3</v>
@@ -4684,18 +4693,18 @@
         <v>0.0919</v>
       </c>
       <c r="I135" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>3.25</v>
@@ -4713,18 +4722,18 @@
         <v>0.1212</v>
       </c>
       <c r="I136" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>3.5</v>
@@ -4742,18 +4751,18 @@
         <v>0.1618</v>
       </c>
       <c r="I137" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>3.75</v>
@@ -4771,18 +4780,18 @@
         <v>0.3568</v>
       </c>
       <c r="I138" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>4</v>
@@ -4800,18 +4809,18 @@
         <v>0.3322</v>
       </c>
       <c r="I139" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>4.25</v>
@@ -4829,18 +4838,18 @@
         <v>0.0685</v>
       </c>
       <c r="I140" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>4.5</v>
@@ -4858,18 +4867,18 @@
         <v>0.1018</v>
       </c>
       <c r="I141" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>4.75</v>
@@ -4887,18 +4896,18 @@
         <v>0.1557</v>
       </c>
       <c r="I142" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>5</v>
@@ -4916,18 +4925,18 @@
         <v>0.2422</v>
       </c>
       <c r="I143" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>5.25</v>
@@ -4945,18 +4954,18 @@
         <v>0.1429</v>
       </c>
       <c r="I144" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>5.5</v>
@@ -4974,18 +4983,18 @@
         <v>0.1964</v>
       </c>
       <c r="I145" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>5.75</v>
@@ -5003,18 +5012,18 @@
         <v>0.1322</v>
       </c>
       <c r="I146" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>6</v>
@@ -5032,18 +5041,18 @@
         <v>0.1181</v>
       </c>
       <c r="I147" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>6.25</v>
@@ -5061,18 +5070,18 @@
         <v>0.8833</v>
       </c>
       <c r="I148" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>6.5</v>
@@ -5090,18 +5099,18 @@
         <v>0.1092</v>
       </c>
       <c r="I149" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>6.75</v>
@@ -5119,18 +5128,18 @@
         <v>0.2869</v>
       </c>
       <c r="I150" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>7</v>
@@ -5148,18 +5157,18 @@
         <v>0.222</v>
       </c>
       <c r="I151" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D152" s="0" t="n">
         <v>1.25</v>
@@ -5182,13 +5191,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D153" s="0" t="n">
         <v>1.5</v>
@@ -5206,18 +5215,18 @@
         <v>0.0024</v>
       </c>
       <c r="I153" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D154" s="0" t="n">
         <v>1.75</v>
@@ -5235,18 +5244,18 @@
         <v>0.0029</v>
       </c>
       <c r="I154" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D155" s="0" t="n">
         <v>2</v>
@@ -5264,18 +5273,18 @@
         <v>0.0127</v>
       </c>
       <c r="I155" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D156" s="0" t="n">
         <v>2.25</v>
@@ -5293,18 +5302,18 @@
         <v>0.0686</v>
       </c>
       <c r="I156" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D157" s="0" t="n">
         <v>2.5</v>
@@ -5322,18 +5331,18 @@
         <v>0.1057</v>
       </c>
       <c r="I157" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B158" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D158" s="0" t="n">
         <v>2.75</v>
@@ -5351,18 +5360,18 @@
         <v>0.2427</v>
       </c>
       <c r="I158" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D159" s="0" t="n">
         <v>3</v>
@@ -5380,18 +5389,18 @@
         <v>0.0919</v>
       </c>
       <c r="I159" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D160" s="0" t="n">
         <v>3.25</v>
@@ -5409,18 +5418,18 @@
         <v>0.079</v>
       </c>
       <c r="I160" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D161" s="0" t="n">
         <v>3.5</v>
@@ -5438,18 +5447,18 @@
         <v>0.1879</v>
       </c>
       <c r="I161" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D162" s="0" t="n">
         <v>4</v>
@@ -5467,18 +5476,18 @@
         <v>0.0933</v>
       </c>
       <c r="I162" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D163" s="0" t="n">
         <v>4.5</v>
@@ -5496,18 +5505,18 @@
         <v>0.1314</v>
       </c>
       <c r="I163" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D164" s="0" t="n">
         <v>5</v>
@@ -5525,18 +5534,18 @@
         <v>0.2584</v>
       </c>
       <c r="I164" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D165" s="0" t="n">
         <v>5.5</v>
@@ -5554,18 +5563,18 @@
         <v>0.1179</v>
       </c>
       <c r="I165" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D166" s="0" t="n">
         <v>6</v>
@@ -5583,18 +5592,18 @@
         <v>0.1948</v>
       </c>
       <c r="I166" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D167" s="0" t="n">
         <v>6.5</v>
@@ -5612,18 +5621,18 @@
         <v>0.1348</v>
       </c>
       <c r="I167" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B168" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D168" s="0" t="n">
         <v>7</v>
@@ -5641,18 +5650,18 @@
         <v>0.2719</v>
       </c>
       <c r="I168" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D169" s="0" t="n">
         <v>4</v>
@@ -5670,18 +5679,18 @@
         <v>0.1343</v>
       </c>
       <c r="I169" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D170" s="0" t="n">
         <v>4.5</v>
@@ -5699,18 +5708,18 @@
         <v>0.1741</v>
       </c>
       <c r="I170" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D171" s="0" t="n">
         <v>5</v>
@@ -5728,18 +5737,18 @@
         <v>0.4131</v>
       </c>
       <c r="I171" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D172" s="0" t="n">
         <v>5.5</v>
@@ -5757,18 +5766,18 @@
         <v>0.1593</v>
       </c>
       <c r="I172" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D173" s="0" t="n">
         <v>6</v>
@@ -5786,18 +5795,18 @@
         <v>0.4367</v>
       </c>
       <c r="I173" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D174" s="0" t="n">
         <v>6.5</v>
@@ -5815,18 +5824,18 @@
         <v>0.8056</v>
       </c>
       <c r="I174" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D175" s="0" t="n">
         <v>7</v>
@@ -5844,18 +5853,18 @@
         <v>0.2069</v>
       </c>
       <c r="I175" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D176" s="0" t="n">
         <v>1.25</v>
@@ -5873,18 +5882,18 @@
         <v>0.0033</v>
       </c>
       <c r="I176" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D177" s="0" t="n">
         <v>1.5</v>
@@ -5902,18 +5911,18 @@
         <v>0.0081</v>
       </c>
       <c r="I177" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D178" s="0" t="n">
         <v>1.75</v>
@@ -5931,18 +5940,18 @@
         <v>0.0092</v>
       </c>
       <c r="I178" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D179" s="0" t="n">
         <v>2</v>
@@ -5960,18 +5969,18 @@
         <v>0.033</v>
       </c>
       <c r="I179" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D180" s="0" t="n">
         <v>2.25</v>
@@ -5994,13 +6003,13 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D181" s="0" t="n">
         <v>2.5</v>
@@ -6018,18 +6027,18 @@
         <v>0.1309</v>
       </c>
       <c r="I181" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D182" s="0" t="n">
         <v>2.75</v>
@@ -6047,18 +6056,18 @@
         <v>0.1327</v>
       </c>
       <c r="I182" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D183" s="0" t="n">
         <v>3</v>
@@ -6076,18 +6085,18 @@
         <v>0.1925</v>
       </c>
       <c r="I183" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D184" s="0" t="n">
         <v>3.25</v>
@@ -6105,18 +6114,18 @@
         <v>0.1089</v>
       </c>
       <c r="I184" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D185" s="0" t="n">
         <v>3.5</v>
@@ -6134,18 +6143,18 @@
         <v>0.2568</v>
       </c>
       <c r="I185" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D186" s="0" t="n">
         <v>4</v>
@@ -6163,18 +6172,18 @@
         <v>0.0794</v>
       </c>
       <c r="I186" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D187" s="0" t="n">
         <v>4.5</v>
@@ -6192,18 +6201,18 @@
         <v>0.1548</v>
       </c>
       <c r="I187" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D188" s="0" t="n">
         <v>5</v>
@@ -6221,18 +6230,18 @@
         <v>0.284</v>
       </c>
       <c r="I188" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D189" s="0" t="n">
         <v>5.5</v>
@@ -6250,18 +6259,18 @@
         <v>0.3891</v>
       </c>
       <c r="I189" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D190" s="0" t="n">
         <v>6</v>
@@ -6279,18 +6288,18 @@
         <v>0.2379</v>
       </c>
       <c r="I190" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D191" s="0" t="n">
         <v>6.5</v>
@@ -6308,18 +6317,18 @@
         <v>0.2096</v>
       </c>
       <c r="I191" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D192" s="0" t="n">
         <v>7</v>
@@ -6337,18 +6346,18 @@
         <v>0.0186</v>
       </c>
       <c r="I192" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D193" s="0" t="n">
         <v>1.2</v>
@@ -6366,18 +6375,18 @@
         <v>0.1109</v>
       </c>
       <c r="I193" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D194" s="0" t="n">
         <v>1.4</v>
@@ -6395,18 +6404,18 @@
         <v>0.0495</v>
       </c>
       <c r="I194" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D195" s="0" t="n">
         <v>1.6</v>
@@ -6424,18 +6433,18 @@
         <v>0.065</v>
       </c>
       <c r="I195" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D196" s="0" t="n">
         <v>1.8</v>
@@ -6453,18 +6462,18 @@
         <v>0.0691</v>
       </c>
       <c r="I196" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D197" s="0" t="n">
         <v>2</v>
@@ -6482,18 +6491,18 @@
         <v>0.0958</v>
       </c>
       <c r="I197" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D198" s="0" t="n">
         <v>2.25</v>
@@ -6511,18 +6520,18 @@
         <v>0.0937</v>
       </c>
       <c r="I198" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D199" s="0" t="n">
         <v>2.5</v>
@@ -6540,18 +6549,18 @@
         <v>0.1093</v>
       </c>
       <c r="I199" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D200" s="0" t="n">
         <v>2.75</v>
@@ -6569,18 +6578,18 @@
         <v>0.0907</v>
       </c>
       <c r="I200" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D201" s="0" t="n">
         <v>3</v>
@@ -6598,18 +6607,18 @@
         <v>0.199</v>
       </c>
       <c r="I201" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D202" s="0" t="n">
         <v>3.25</v>
@@ -6627,18 +6636,18 @@
         <v>0.0807</v>
       </c>
       <c r="I202" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D203" s="0" t="n">
         <v>3.5</v>
@@ -6656,7 +6665,7 @@
         <v>0.0394</v>
       </c>
       <c r="I203" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
